--- a/outputs_xlsx_solution/prog-noloop.2-wide.xlsx
+++ b/outputs_xlsx_solution/prog-noloop.2-wide.xlsx
@@ -65,7 +65,7 @@
     <t>fld F0, 0(X1)</t>
   </si>
   <si>
-    <t>IS/EX</t>
+    <t>EX</t>
   </si>
   <si>
     <t>fmul F0, F0, F2</t>
@@ -74,10 +74,10 @@
     <t>fld F4, 0(X2)</t>
   </si>
   <si>
-    <t>WB/CT</t>
-  </si>
-  <si>
-    <t>EX</t>
+    <t>WB</t>
+  </si>
+  <si>
+    <t>CT</t>
   </si>
   <si>
     <t>fadd F0, F0, F4</t>
@@ -86,6 +86,9 @@
     <t>fsd F0, 0(X2)</t>
   </si>
   <si>
+    <t>IS</t>
+  </si>
+  <si>
     <t>addi X1, X1, -8</t>
   </si>
   <si>
@@ -101,13 +104,34 @@
     <t>Instruction Decode</t>
   </si>
   <si>
-    <t>Add to Issue Queue/Execute (if instruction is ready, it can start executing in the same cycle it is added to issue queue)</t>
-  </si>
-  <si>
-    <t>Execute</t>
-  </si>
-  <si>
-    <t>Write Back/Commit (instruction can be committed on the same cycle it writes back)</t>
+    <t>Add to Issue Queue</t>
+  </si>
+  <si>
+    <t>Execute (instruction can execute on the same cycle as it is added to the issue queue, if it is ready)</t>
+  </si>
+  <si>
+    <t>Write Back</t>
+  </si>
+  <si>
+    <t>Commit (instruction can commit on the same cycle as write back, if at the head)</t>
+  </si>
+  <si>
+    <t>RS Stall</t>
+  </si>
+  <si>
+    <t>Reservation Station Stall (stalled because reservation stations are full)</t>
+  </si>
+  <si>
+    <t>ROB Stall</t>
+  </si>
+  <si>
+    <t>Reorder Buffer Stall (stalled because the ROB is full)</t>
+  </si>
+  <si>
+    <t>CDB Stall</t>
+  </si>
+  <si>
+    <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
   </si>
 </sst>
 </file>
@@ -516,6 +540,9 @@
       <c r="Q1">
         <v>14</v>
       </c>
+      <c r="R1">
+        <v>15</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -537,7 +564,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -560,10 +587,10 @@
         <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -586,7 +613,7 @@
         <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -609,10 +636,10 @@
         <v>10</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -632,22 +659,22 @@
         <v>7</v>
       </c>
       <c r="H6" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -670,13 +697,13 @@
         <v>10</v>
       </c>
       <c r="I7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J7" t="s">
         <v>13</v>
       </c>
       <c r="M7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -696,19 +723,19 @@
         <v>7</v>
       </c>
       <c r="I8" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="M8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="N8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="P8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -728,13 +755,13 @@
         <v>7</v>
       </c>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="P9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -745,7 +772,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H10" t="s">
         <v>5</v>
@@ -760,7 +787,7 @@
         <v>13</v>
       </c>
       <c r="Q10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -771,7 +798,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H11" t="s">
         <v>5</v>
@@ -783,18 +810,18 @@
         <v>10</v>
       </c>
       <c r="K11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L11" t="s">
         <v>13</v>
       </c>
-      <c r="Q11" t="s">
-        <v>13</v>
+      <c r="R11" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -802,7 +829,7 @@
         <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -810,23 +837,23 @@
         <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -834,7 +861,31 @@
         <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/outputs_xlsx_solution/prog-noloop.2-wide.xlsx
+++ b/outputs_xlsx_solution/prog-noloop.2-wide.xlsx
@@ -68,6 +68,9 @@
     <t>EX</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>fmul F0, F0, F2</t>
   </si>
   <si>
@@ -132,6 +135,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -564,7 +570,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -584,13 +590,13 @@
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
         <v>10</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -613,7 +619,7 @@
         <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -633,13 +639,13 @@
         <v>7</v>
       </c>
       <c r="G5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H5" t="s">
         <v>10</v>
       </c>
       <c r="I5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -650,7 +656,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
         <v>5</v>
@@ -659,7 +665,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6" t="s">
         <v>10</v>
@@ -674,7 +680,7 @@
         <v>10</v>
       </c>
       <c r="M6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -685,7 +691,7 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F7" t="s">
         <v>5</v>
@@ -694,16 +700,16 @@
         <v>7</v>
       </c>
       <c r="H7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I7" t="s">
         <v>10</v>
       </c>
       <c r="J7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -714,7 +720,7 @@
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G8" t="s">
         <v>5</v>
@@ -723,7 +729,7 @@
         <v>7</v>
       </c>
       <c r="I8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M8" t="s">
         <v>10</v>
@@ -735,7 +741,7 @@
         <v>10</v>
       </c>
       <c r="P8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -746,7 +752,7 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9" t="s">
         <v>5</v>
@@ -755,13 +761,13 @@
         <v>7</v>
       </c>
       <c r="I9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P9" t="s">
         <v>10</v>
       </c>
       <c r="Q9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -772,7 +778,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H10" t="s">
         <v>5</v>
@@ -784,10 +790,10 @@
         <v>10</v>
       </c>
       <c r="K10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -798,7 +804,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H11" t="s">
         <v>5</v>
@@ -807,21 +813,21 @@
         <v>7</v>
       </c>
       <c r="J11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K11" t="s">
         <v>10</v>
       </c>
       <c r="L11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -829,7 +835,7 @@
         <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -837,15 +843,15 @@
         <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -853,39 +859,55 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" t="s">
         <v>31</v>
       </c>
-      <c r="B21" t="s">
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
         <v>32</v>
+      </c>
+      <c r="B22" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
